--- a/employee_surveys/010_organizational_fairness_perception_survey--employee_surveys.xlsx
+++ b/employee_surveys/010_organizational_fairness_perception_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -757,29 +757,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>diversity_and_inclusion</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Diversity and Inclusion</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>diversity_and_inclusion_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>diversity_and_inclusion</t>
+          <t>internal_communication</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diversity and Inclusion</t>
+          <t>Internal communication</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>internal_communication</t>
+          <t>external_communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Internal communication</t>
+          <t>External communication</t>
         </is>
       </c>
     </row>
@@ -808,29 +808,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>external_communication</t>
+          <t>communication_with_leadership</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>External communication</t>
+          <t>Communication with leadership</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>work_life_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>communication_with_leadership</t>
+          <t>work-life_balance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Communication with leadership</t>
+          <t>Work-life balance</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work-life_balance</t>
+          <t>family_life</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Work-life balance</t>
+          <t>Family life</t>
         </is>
       </c>
     </row>
@@ -859,29 +859,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>family_life</t>
+          <t>wellness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Family life</t>
+          <t>Wellness</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>work_life_choices</t>
+          <t>fair_compens_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>wellness</t>
+          <t>salary_and_wages</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wellness</t>
+          <t>Salary and wages</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>salary_and_wages</t>
+          <t>bennies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salary and wages</t>
+          <t>Bennies</t>
         </is>
       </c>
     </row>
@@ -910,29 +910,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bennies</t>
+          <t>stock_options</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bennies</t>
+          <t>Stock options</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fair_compens_choices</t>
+          <t>promotion_opportunities_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>stock_options</t>
+          <t>opportunities_for_advancement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Stock options</t>
+          <t>Opportunities for advancement</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>opportunities_for_advancement</t>
+          <t>opportunities_for_growth</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Opportunities for advancement</t>
+          <t>Opportunities for growth</t>
         </is>
       </c>
     </row>
@@ -961,27 +961,10 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>opportunities_for_growth</t>
+          <t>opportunities_for_development</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>Opportunities for growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>promotion_opportunities_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>opportunities_for_development</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t>Opportunities for development</t>
         </is>
